--- a/画面遷移図.xlsx
+++ b/画面遷移図.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wakitakouhei/勉強/Portfolio/HomeStockManager/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BF3EFE-CD49-FF46-99E9-ECDC6722F20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CF135D-1FAE-BA42-BFA1-98CB09354A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{A070457D-3714-924F-832C-E90D09F1E1B0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{A070457D-3714-924F-832C-E90D09F1E1B0}"/>
   </bookViews>
   <sheets>
     <sheet name="画面名" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="15">
   <si>
     <t>画面名</t>
     <rPh sb="0" eb="3">
@@ -96,17 +96,6 @@
   </si>
   <si>
     <t>・設定画面</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>※管理物の消費期限が近づいたら、色がつく</t>
-    <rPh sb="1" eb="4">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　色がついた日付をクリックすると、ポップアップ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1816,16 +1805,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1840,8 +1829,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2171700" y="1651000"/>
-          <a:ext cx="8470900" cy="4546600"/>
+          <a:off x="2997200" y="1206500"/>
+          <a:ext cx="7112000" cy="5689600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1877,8 +1866,68 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>カレンダー</a:t>
+            <a:t>買い物メモ</a:t>
           </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>今週切れそうなもの</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>来週切れそうなもの</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5657,7 +5706,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -5700,27 +5749,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4062E8-D283-4948-8BB3-D1B51B43767D}">
-  <dimension ref="P2:P22"/>
+  <dimension ref="P4:P22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="16:16">
-      <c r="P2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="16:16">
-      <c r="P3" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="4" spans="16:16">
       <c r="P4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="16:16">
       <c r="P19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="16:16">
@@ -5730,12 +5769,12 @@
     </row>
     <row r="21" spans="16:16">
       <c r="P21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="16:16">
       <c r="P22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -5752,7 +5791,7 @@
   <sheetData>
     <row r="4" spans="16:16">
       <c r="P4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="16:16">
@@ -5762,12 +5801,12 @@
     </row>
     <row r="6" spans="16:16">
       <c r="P6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="16:16">
       <c r="P7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -5784,7 +5823,7 @@
   <sheetData>
     <row r="2" spans="16:16">
       <c r="P2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="16:16">
@@ -5794,7 +5833,7 @@
     </row>
     <row r="4" spans="16:16">
       <c r="P4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="16:16">
@@ -5804,12 +5843,12 @@
     </row>
     <row r="6" spans="16:16">
       <c r="P6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="16:16">
       <c r="P18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5826,7 +5865,7 @@
   <sheetData>
     <row r="2" spans="16:16">
       <c r="P2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="16:16">
@@ -5836,7 +5875,7 @@
     </row>
     <row r="4" spans="16:16">
       <c r="P4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="16:16">
@@ -5846,7 +5885,7 @@
     </row>
     <row r="6" spans="16:16">
       <c r="P6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -5863,7 +5902,7 @@
   <sheetData>
     <row r="2" spans="16:16">
       <c r="P2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="16:16">
@@ -5873,7 +5912,7 @@
     </row>
     <row r="4" spans="16:16">
       <c r="P4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="16:16">
@@ -5883,7 +5922,7 @@
     </row>
     <row r="6" spans="16:16">
       <c r="P6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -5900,17 +5939,17 @@
   <sheetData>
     <row r="6" spans="16:16">
       <c r="P6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="16:16">
       <c r="P7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="16:16">
       <c r="P8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="16:16">

--- a/画面遷移図.xlsx
+++ b/画面遷移図.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wakitakouhei/勉強/Portfolio/HomeStockManager/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CF135D-1FAE-BA42-BFA1-98CB09354A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34577876-0E4C-724A-944B-D8E2829445BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{A070457D-3714-924F-832C-E90D09F1E1B0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{A070457D-3714-924F-832C-E90D09F1E1B0}"/>
   </bookViews>
   <sheets>
     <sheet name="画面名" sheetId="1" r:id="rId1"/>
@@ -204,13 +204,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>584200</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>254000</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
@@ -281,13 +281,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>558800</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
@@ -358,13 +358,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>50800</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>673100</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
@@ -435,13 +435,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>368300</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
@@ -512,13 +512,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>431800</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>101600</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -589,13 +589,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>711200</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
@@ -666,13 +666,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>215900</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>723900</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
@@ -726,13 +726,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>901700</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>215900</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -786,13 +786,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>863600</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>177800</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
@@ -846,13 +846,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>711200</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>215900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>215900</xdr:rowOff>
@@ -906,13 +906,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -966,13 +966,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>355600</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1043,13 +1043,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>927089</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>69414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>439203</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>69414</xdr:rowOff>
@@ -1103,13 +1103,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>241300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>165100</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>241300</xdr:rowOff>
